--- a/referentiel/referentiel_irrigation.xlsx
+++ b/referentiel/referentiel_irrigation.xlsx
@@ -22593,7 +22593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -23078,51 +23078,51 @@
     <row r="10" ht="27.6" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>Forage individuel</t>
+          <t>Pompage sur cours d'eau</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>distance_amenee</t>
+          <t>capex_station</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>Distance entre la source et la parcelle (réseau d'amenée)</t>
+          <t>Station de pompage (pompe, crépine, génie civil)</t>
         </is>
       </c>
       <c r="D10" s="36" t="n">
-        <v>500</v>
+        <v>25000</v>
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>€</t>
         </is>
       </c>
       <c r="F10" s="18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G10" s="18" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H10" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="56" t="n">
-        <v>20000</v>
+      <c r="I10" s="18" t="n">
+        <v>500000</v>
       </c>
       <c r="J10" s="18" t="inlineStr">
         <is>
-          <t>SGPE_2026</t>
+          <t>CDAF_2025</t>
         </is>
       </c>
       <c r="K10" s="18" t="inlineStr">
         <is>
-          <t>Hypothèse de travail. CRA 71 (2024) : 800 m (10 ha) à 1 600 m (25 ha) de tuyaux ; CA Hauts-de-France (2023) : parcelles à 1 000–2 000 m du point d'eau ; CDAF (2025) : exemples avec 3 000 m d'enterré.</t>
+          <t>APCA/CA Loiret 2025 : pompe de surface 50 ch/50 m³/h + accessoires + montage + compteur ≈ 25 000 € ; 100 ch/100 m³/h ≈ 45 000 €. Crépine et génie civil inclus. Valeur retenue 25 000 € cohérente (50 m³/h).</t>
         </is>
       </c>
     </row>
@@ -23134,76 +23134,76 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>capex_station</t>
+          <t>duree_vie</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>Station de pompage (pompe, crépine, génie civil)</t>
+          <t>Durée de vie</t>
         </is>
       </c>
       <c r="D11" s="36" t="n">
-        <v>25000</v>
+        <v>30</v>
       </c>
       <c r="E11" s="18" t="inlineStr">
         <is>
-          <t>€</t>
+          <t>ans</t>
         </is>
       </c>
       <c r="F11" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G11" s="18" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H11" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>500000</v>
+        <v>1</v>
+      </c>
+      <c r="I11" s="56" t="n">
+        <v>80</v>
       </c>
       <c r="J11" s="18" t="inlineStr">
         <is>
-          <t>CDAF_2025</t>
+          <t>SGPE_2026</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
         <is>
-          <t>APCA/CA Loiret 2025 : pompe de surface 50 ch/50 m³/h + accessoires + montage + compteur ≈ 25 000 € ; 100 ch/100 m³/h ≈ 45 000 €. Crépine et génie civil inclus. Valeur retenue 25 000 € cohérente (50 m³/h).</t>
+          <t>Valeur par défaut retenue. APCA/CA Loiret 2025 amortit la station d'irrigation sur 20 ans (linéaire, valeur vénale nulle)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="27.6" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>Pompage sur cours d'eau</t>
+          <t>Retenue collinaire</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>duree_vie</t>
+          <t>cout_stockage</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>Durée de vie</t>
+          <t>Coût de construction</t>
         </is>
       </c>
       <c r="D12" s="36" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>ans</t>
+          <t>€/m³ stocké</t>
         </is>
       </c>
       <c r="F12" s="18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G12" s="18" t="inlineStr">
@@ -23212,44 +23212,44 @@
         </is>
       </c>
       <c r="H12" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="56" t="n">
-        <v>80</v>
+        <v>0</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>50</v>
       </c>
       <c r="J12" s="18" t="inlineStr">
         <is>
-          <t>SGPE_2026</t>
+          <t>LOUBIER_2026</t>
         </is>
       </c>
       <c r="K12" s="18" t="inlineStr">
         <is>
-          <t>Valeur par défaut retenue. APCA/CA Loiret 2025 amortit la station d'irrigation sur 20 ans (linéaire, valeur vénale nulle)</t>
+          <t>8 €/m³ retenu d'après le témoignage de Sébastien Loubier (LOUBIER_2026) : prix compris entre 6 et 12 €/m³ selon le type d'ouvrage, plus faible pour les retenues collinaires avec peu de travaux de terrassement. Cohérent avec 4 à 8 €/m³ selon Terre-net (2022).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26.4" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>Pompage sur cours d'eau</t>
+          <t>Retenue collinaire</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>distance_amenee</t>
+          <t>duree_vie</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>Distance entre la source et la parcelle (réseau d'amenée)</t>
+          <t>Durée de vie</t>
         </is>
       </c>
       <c r="D13" s="36" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ans</t>
         </is>
       </c>
       <c r="F13" s="18" t="inlineStr">
@@ -23263,10 +23263,10 @@
         </is>
       </c>
       <c r="H13" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="56" t="n">
-        <v>20000</v>
+        <v>80</v>
       </c>
       <c r="J13" s="18" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
       </c>
       <c r="K13" s="18" t="inlineStr">
         <is>
-          <t>Hypothèse de travail : distance entre la station de pompage en berge et la parcelle.</t>
+          <t>Valeur par défaut retenue</t>
         </is>
       </c>
     </row>
@@ -23287,76 +23287,76 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>cout_stockage</t>
+          <t>part_remplissage_pompe</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>Coût de construction</t>
+          <t>Part du remplissage assurée par pompage</t>
         </is>
       </c>
       <c r="D14" s="36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E14" s="18" t="inlineStr">
         <is>
-          <t>€/m³ stocké</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F14" s="18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G14" s="18" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H14" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="18" t="n">
-        <v>50</v>
+      <c r="I14" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="J14" s="18" t="inlineStr">
         <is>
-          <t>LOUBIER_2026</t>
+          <t>SGPE_2026</t>
         </is>
       </c>
       <c r="K14" s="18" t="inlineStr">
         <is>
-          <t>8 €/m³ retenu d'après le témoignage de Sébastien Loubier (LOUBIER_2026) : prix compris entre 6 et 12 €/m³ selon le type d'ouvrage, plus faible pour les retenues collinaires avec peu de travaux de terrassement. Cohérent avec 4 à 8 €/m³ selon Terre-net (2022).</t>
+          <t>Retenue alimentée uniquement par ruissellement et précipitations (remplissage gravitaire) : aucune énergie de remplissage. Seule la reprise vers la parcelle est pompée. Redevance de prélèvement due au tarif de catégorie 1, même en ZRE (art. L213-10-9 du Code de l'environnement).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="39.6" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>Retenue collinaire</t>
+          <t>Retenue par pompage</t>
         </is>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>duree_vie</t>
+          <t>cout_stockage</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>Durée de vie</t>
+          <t>Coût de construction</t>
         </is>
       </c>
       <c r="D15" s="36" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E15" s="18" t="inlineStr">
         <is>
-          <t>ans</t>
+          <t>€/m³ stocké</t>
         </is>
       </c>
       <c r="F15" s="18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G15" s="18" t="inlineStr">
@@ -23365,61 +23365,61 @@
         </is>
       </c>
       <c r="H15" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="56" t="n">
-        <v>80</v>
+        <v>0</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>50</v>
       </c>
       <c r="J15" s="18" t="inlineStr">
         <is>
-          <t>SGPE_2026</t>
+          <t>LOUBIER_2026</t>
         </is>
       </c>
       <c r="K15" s="18" t="inlineStr">
         <is>
-          <t>Valeur par défaut retenue</t>
+          <t>12 €/m³ retenu d'après le témoignage de Sébastien Loubier (LOUBIER_2026), haut de la fourchette 6-12 €/m³ pour une retenue avec pompage (terrassement et pompage de remplissage plus coûteux). Cohérent avec Aubertin et al. (2023) : 12,25 €/m³ (16 réserves de 6,2 Mm³ pour un coût total de 76 M€, actualisation sept. 2022, remplissage hivernal par pompage) ; borne basse 8,36 €/m³ (2,3 M€ / 275 000 m³, Dordogne).</t>
         </is>
       </c>
     </row>
     <row r="16" hidden="1" ht="26.4" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>Retenue collinaire</t>
+          <t>Retenue par pompage</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>part_remplissage_pompe</t>
+          <t>duree_vie</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>Part du remplissage assurée par pompage</t>
+          <t>Durée de vie</t>
         </is>
       </c>
       <c r="D16" s="36" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E16" s="18" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ans</t>
         </is>
       </c>
       <c r="F16" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G16" s="18" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H16" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="56" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="J16" s="18" t="inlineStr">
         <is>
@@ -23428,32 +23428,32 @@
       </c>
       <c r="K16" s="18" t="inlineStr">
         <is>
-          <t>Retenue alimentée uniquement par ruissellement et précipitations (remplissage gravitaire) : aucune énergie de remplissage. Seule la reprise vers la parcelle est pompée.</t>
+          <t>Valeur par défaut retenue</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26.4" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>Retenue collinaire</t>
+          <t>Retenue par pompage</t>
         </is>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>distance_amenee</t>
+          <t>part_remplissage_pompe</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>Distance entre la source et la parcelle (réseau d'amenée)</t>
-        </is>
-      </c>
-      <c r="D17" s="36" t="n">
-        <v>500</v>
+          <t>Part du remplissage assurée par pompage</t>
+        </is>
+      </c>
+      <c r="D17" s="66" t="n">
+        <v>0.95</v>
       </c>
       <c r="E17" s="18" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F17" s="18" t="inlineStr">
@@ -23470,7 +23470,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="56" t="n">
-        <v>20000</v>
+        <v>1</v>
       </c>
       <c r="J17" s="18" t="inlineStr">
         <is>
@@ -23479,185 +23479,185 @@
       </c>
       <c r="K17" s="18" t="inlineStr">
         <is>
-          <t>Hypothèse de travail : distance entre la retenue et la parcelle.</t>
+          <t>Hypothèse. Remplissage hivernal par pompage (nappe ou cours d'eau), complété par la pluie tombant directement sur le plan d'eau : ≈ 0,3–0,4 m de pluie d'hiver pour 8 à 10 m de hauteur d'eau utile, soit ≈ 5 % du volume. Le volume pompé en hiver est ensuite repompé en été vers la parcelle.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="41.4" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>Retenue par pompage</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>cout_stockage</t>
+          <t>capex_branchement</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>Coût de construction</t>
+          <t>Adhésion et branchement</t>
         </is>
       </c>
       <c r="D18" s="36" t="n">
-        <v>12</v>
+        <v>6000</v>
       </c>
       <c r="E18" s="18" t="inlineStr">
         <is>
-          <t>€/m³ stocké</t>
+          <t>€</t>
         </is>
       </c>
       <c r="F18" s="18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G18" s="18" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H18" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="18" t="n">
-        <v>50</v>
+      <c r="I18" s="56" t="n">
+        <v>200000</v>
       </c>
       <c r="J18" s="18" t="inlineStr">
         <is>
-          <t>LOUBIER_2026</t>
+          <t>SGPE_2026</t>
         </is>
       </c>
       <c r="K18" s="18" t="inlineStr">
         <is>
-          <t>12 €/m³ retenu d'après le témoignage de Sébastien Loubier (LOUBIER_2026), haut de la fourchette 6-12 €/m³ pour une retenue avec pompage (terrassement et pompage de remplissage plus coûteux). Cohérent avec Aubertin et al. (2023) : 12,25 €/m³ (16 réserves de 6,2 Mm³ pour un coût total de 76 M€, actualisation sept. 2022, remplissage hivernal par pompage) ; borne basse 8,36 €/m³ (2,3 M€ / 275 000 m³, Dordogne).</t>
+          <t>Adhésion + branchement à l'ASA. À consolider. CRA 71 2024 : plafond d'aide FranceAgriMer relevé à 150 000 € HT pour les CUMA/ASA (contre 40 000 € par exploitation).</t>
         </is>
       </c>
     </row>
     <row r="19" hidden="1" ht="27.6" customHeight="1">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>Retenue par pompage</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>duree_vie</t>
+          <t>part_fixe</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>Durée de vie</t>
+          <t>Part fixe</t>
         </is>
       </c>
       <c r="D19" s="36" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>ans</t>
+          <t>€/ha/an</t>
         </is>
       </c>
       <c r="F19" s="18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G19" s="18" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H19" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="56" t="n">
-        <v>80</v>
+        <v>0</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>2000</v>
       </c>
       <c r="J19" s="18" t="inlineStr">
         <is>
-          <t>SGPE_2026</t>
+          <t>REUSSIR_2026</t>
         </is>
       </c>
       <c r="K19" s="18" t="inlineStr">
         <is>
-          <t>Valeur par défaut retenue</t>
+          <t>360 € par module de 2 000 m³, ramenés à l'hectare (Réussir, 2026). Contrôle de cohérence : part fixe 180 €/ha + part volumétrique 0,13 €/m³ × 2 500 m³/ha = 505 €/ha, dans la fourchette de 430 à 710 €/ha pour 2 500 m³/ha relevée pour les ASA (repère à sourcer). AEAG (2022) : exemple d'ASA à 235 €/ha de charges fixes et 0,31 €/m³ tout compris.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26.4" customHeight="1">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>Retenue par pompage</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>part_remplissage_pompe</t>
+          <t>part_volumetrique</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>Part du remplissage assurée par pompage</t>
-        </is>
-      </c>
-      <c r="D20" s="66" t="n">
-        <v>0.95</v>
+          <t>Part volumétrique</t>
+        </is>
+      </c>
+      <c r="D20" s="36" t="n">
+        <v>0.13</v>
       </c>
       <c r="E20" s="18" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>€/m³</t>
         </is>
       </c>
       <c r="F20" s="18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G20" s="18" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H20" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="56" t="n">
-        <v>1</v>
+      <c r="I20" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="J20" s="18" t="inlineStr">
         <is>
-          <t>SGPE_2026</t>
+          <t>REUSSIR_2026</t>
         </is>
       </c>
       <c r="K20" s="18" t="inlineStr">
         <is>
-          <t>Hypothèse. Remplissage hivernal par pompage (nappe ou cours d'eau), complété par la pluie tombant directement sur le plan d'eau : ≈ 0,3–0,4 m de pluie d'hiver pour 8 à 10 m de hauteur d'eau utile, soit ≈ 5 % du volume. Le volume pompé en hiver est ensuite repompé en été vers la parcelle.</t>
+          <t>Charges variables (électricité de pompage) de l'ASA. Cohérent avec le coût d'énergie APCA/CA Loiret 2025 (≈ 0,118 €/m³ pour une station d'irrigation).</t>
         </is>
       </c>
     </row>
     <row r="21" hidden="1" ht="55.2" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>Retenue par pompage</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>distance_amenee</t>
+          <t>duree_vie</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>Distance entre la source et la parcelle (réseau d'amenée)</t>
+          <t>Durée de vie</t>
         </is>
       </c>
       <c r="D21" s="36" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ans</t>
         </is>
       </c>
       <c r="F21" s="18" t="inlineStr">
@@ -23671,10 +23671,10 @@
         </is>
       </c>
       <c r="H21" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="56" t="n">
-        <v>20000</v>
+        <v>80</v>
       </c>
       <c r="J21" s="18" t="inlineStr">
         <is>
@@ -23683,185 +23683,185 @@
       </c>
       <c r="K21" s="18" t="inlineStr">
         <is>
-          <t>Hypothèse de travail : distance entre la retenue et la parcelle.</t>
+          <t>Valeur par défaut retenue. Repère APCA/CA Loiret 2025 : station d'irrigation amortie sur 20 ans, réseaux enterrés 30 ans.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="39.6" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>capex_branchement</t>
+          <t>cout_tuyau_ml</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>Adhésion et branchement</t>
+          <t>Coût des tuyaux (fourniture et pose)</t>
         </is>
       </c>
       <c r="D22" s="36" t="n">
-        <v>6000</v>
+        <v>20</v>
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>€</t>
+          <t>€/m</t>
         </is>
       </c>
       <c r="F22" s="18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G22" s="18" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="56" t="n">
-        <v>200000</v>
+        <v>10</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>60</v>
       </c>
       <c r="J22" s="18" t="inlineStr">
         <is>
-          <t>SGPE_2026</t>
+          <t>CDAF_2025</t>
         </is>
       </c>
       <c r="K22" s="18" t="inlineStr">
         <is>
-          <t>Adhésion + branchement à l'ASA. À consolider. CRA 71 2024 : plafond d'aide FranceAgriMer relevé à 150 000 € HT pour les CUMA/ASA (contre 40 000 € par exploitation).</t>
+          <t>Canalisation fixe enterrée Ø140 mm (60 m³/h), fournie et posée (tranchée, bouches, accès) : 20 €/m, amortie 30 ans — CDAF (2025), cohérent avec la station de pompage 50 m³/h retenue. Autres diamètres CDAF 2025 : Ø160 23 €/m, Ø200 29 €/m, Ø250 45 €/m. Repères : CRA Oise (2023) 19,6–40,5 €/m ; CDAF (2020) 15,6–32,1 €/m ; CA Hauts-de-France (2023) 21–25 €/m ; PSN Corse (2025) 20 €/ml hors pose ; CRA 71 (2024) 12 €/ml ; tuyaux alu mobiles 10,7–14,2 €/m.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="27.6" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>part_fixe</t>
+          <t>distance_amenee</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>Part fixe</t>
+          <t>Distance entre la source et la parcelle (réseau d'amenée)</t>
         </is>
       </c>
       <c r="D23" s="36" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
-          <t>€/ha/an</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F23" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G23" s="18" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H23" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="18" t="n">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="J23" s="18" t="inlineStr">
         <is>
-          <t>REUSSIR_2026</t>
+          <t>SGPE_2026</t>
         </is>
       </c>
       <c r="K23" s="18" t="inlineStr">
         <is>
-          <t>360 € par module de 2 000 m³, ramenés à l'hectare (Réussir, 2026). Contrôle de cohérence : part fixe 180 €/ha + part volumétrique 0,13 €/m³ × 2 500 m³/ha = 505 €/ha, dans la fourchette de 430 à 710 €/ha pour 2 500 m³/ha relevée pour les ASA (repère à sourcer). AEAG (2022) : exemple d'ASA à 235 €/ha de charges fixes et 0,31 €/m³ tout compris.</t>
+          <t>Hypothèse de travail commune à tous les types d'accès, sauf l'ASA (eau livrée à une borne en bord de parcelle). Repères : CRA 71 (2024) 800 m (10 ha) à 1 600 m (25 ha) de tuyaux ; CA Hauts-de-France (2023) parcelles à 1 000–2 000 m du point d'eau. La colonne d'exhaure du forage est comprise dans la station de pompage.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="27.6" customHeight="1">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>part_volumetrique</t>
+          <t>duree_vie_reseau</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>Part volumétrique</t>
+          <t>Durée de vie du réseau d'amenée</t>
         </is>
       </c>
       <c r="D24" s="36" t="n">
-        <v>0.13</v>
+        <v>30</v>
       </c>
       <c r="E24" s="18" t="inlineStr">
         <is>
-          <t>€/m³</t>
+          <t>ans</t>
         </is>
       </c>
       <c r="F24" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G24" s="18" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H24" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="I24" s="56" t="n">
+        <v>80</v>
       </c>
       <c r="J24" s="18" t="inlineStr">
         <is>
-          <t>REUSSIR_2026</t>
+          <t>SGPE_2026</t>
         </is>
       </c>
       <c r="K24" s="18" t="inlineStr">
         <is>
-          <t>Charges variables (électricité de pompage) de l'ASA. Cohérent avec le coût d'énergie APCA/CA Loiret 2025 (≈ 0,118 €/m³ pour une station d'irrigation).</t>
+          <t>Valeur par défaut retenue</t>
         </is>
       </c>
     </row>
     <row r="25" hidden="1" ht="26.4" customHeight="1">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>duree_vie</t>
+          <t>taux_actualisation</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>Durée de vie</t>
+          <t>Taux d'actualisation de l'accès à la ressource</t>
         </is>
       </c>
       <c r="D25" s="36" t="n">
-        <v>30</v>
+        <v>0.03</v>
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>ans</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F25" s="18" t="inlineStr">
@@ -23875,10 +23875,10 @@
         </is>
       </c>
       <c r="H25" s="18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="56" t="n">
-        <v>80</v>
+        <v>0.15</v>
       </c>
       <c r="J25" s="18" t="inlineStr">
         <is>
@@ -23887,32 +23887,32 @@
       </c>
       <c r="K25" s="18" t="inlineStr">
         <is>
-          <t>Valeur par défaut retenue. Repère APCA/CA Loiret 2025 : station d'irrigation amortie sur 20 ans, réseaux enterrés 30 ans.</t>
+          <t>Sert au facteur d'annualisation ; 0 % = amortissement linéaire</t>
         </is>
       </c>
     </row>
     <row r="26" ht="55.2" customHeight="1">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>Général</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>distance_amenee</t>
+          <t>taux_subvention</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>Distance entre la source et la parcelle (réseau d'amenée)</t>
-        </is>
-      </c>
-      <c r="D26" s="36" t="n">
-        <v>0</v>
+          <t>Subvention publique aux infrastructures d'accès</t>
+        </is>
+      </c>
+      <c r="D26" s="67" t="n">
+        <v>0.7</v>
       </c>
       <c r="E26" s="18" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F26" s="18" t="inlineStr">
@@ -23928,17 +23928,17 @@
       <c r="H26" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="18" t="n">
-        <v>20000</v>
+      <c r="I26" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="J26" s="18" t="inlineStr">
         <is>
-          <t>AUBERTIN_2023</t>
+          <t>SGPE_2026</t>
         </is>
       </c>
       <c r="K26" s="18" t="inlineStr">
         <is>
-          <t>L'ASA livre l'eau sous pression en bord de champ (Aubertin et al., 2023) : pas de réseau d'amenée à la charge de l'adhérent. À renseigner si la borne est éloignée.</t>
+          <t>Défaut retenu pour les retenues (collinaire, pompage), le pompage sur cours d'eau, le réseau collectif et l'ASA. Un taux documenté de 45 % s'applique spécifiquement au forage individuel (voir ligne « Forage individuel »). Aides recensées CRA 71 2024 : PCAE petits équipements 40 % (+10 % JA/bio ; 400–5 000 €) ; PSN stockage d'eau 40 % ; FranceAgriMer sécheresse 30 % (+10 % JA/CUMA ; plafond 40 000 €, 150 000 € CUMA/ASA) ; CUCM forage/retenue 40 % (plafond 18 000 € HT) ; récupérateurs d'eau dépt. 71 65 % (plafond 35 000 €).</t>
         </is>
       </c>
     </row>
@@ -23950,25 +23950,25 @@
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>cout_tuyau_ml</t>
+          <t>taux_remplissage</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>Coût des tuyaux (fourniture et pose)</t>
-        </is>
-      </c>
-      <c r="D27" s="36" t="n">
-        <v>20</v>
+          <t>Taux de remplissage d'une retenue</t>
+        </is>
+      </c>
+      <c r="D27" s="66" t="n">
+        <v>1</v>
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
-          <t>€/m</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F27" s="18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G27" s="18" t="inlineStr">
@@ -23977,222 +23977,22 @@
         </is>
       </c>
       <c r="H27" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="I27" s="18" t="n">
-        <v>60</v>
+        <v>0</v>
+      </c>
+      <c r="I27" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="J27" s="18" t="inlineStr">
         <is>
-          <t>CDAF_2025</t>
-        </is>
-      </c>
-      <c r="K27" s="18" t="inlineStr">
-        <is>
-          <t>Canalisation fixe enterrée Ø140 mm (60 m³/h), fournie et posée (tranchée, bouches, accès) : 20 €/m, amortie 30 ans — CDAF (2025), cohérent avec la station de pompage 50 m³/h retenue. Autres diamètres CDAF 2025 : Ø160 23 €/m, Ø200 29 €/m, Ø250 45 €/m. Repères : CRA Oise (2023) 19,6–40,5 €/m ; CDAF (2020) 15,6–32,1 €/m ; CA Hauts-de-France (2023) 21–25 €/m ; PSN Corse (2025) 20 €/ml hors pose ; CRA 71 (2024) 12 €/ml ; tuyaux alu mobiles 10,7–14,2 €/m.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="27.6" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>Général</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>duree_vie_reseau</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>Durée de vie du réseau d'amenée</t>
-        </is>
-      </c>
-      <c r="D28" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>ans</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="56" t="n">
-        <v>80</v>
-      </c>
-      <c r="J28" s="18" t="inlineStr">
-        <is>
           <t>SGPE_2026</t>
         </is>
       </c>
-      <c r="K28" s="18" t="inlineStr">
-        <is>
-          <t>Valeur par défaut retenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="27.6" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>Général</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>taux_actualisation</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>Taux d'actualisation de l'accès à la ressource</t>
-        </is>
-      </c>
-      <c r="D29" s="36" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H29" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="56" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J29" s="18" t="inlineStr">
-        <is>
-          <t>SGPE_2026</t>
-        </is>
-      </c>
-      <c r="K29" s="18" t="inlineStr">
-        <is>
-          <t>Sert au facteur d'annualisation ; 0 % = amortissement linéaire</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" hidden="1" ht="96.59999999999999" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>Général</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>taux_subvention</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>Subvention publique aux infrastructures d'accès</t>
-        </is>
-      </c>
-      <c r="D30" s="67" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G30" s="18" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H30" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="18" t="inlineStr">
-        <is>
-          <t>SGPE_2026</t>
-        </is>
-      </c>
-      <c r="K30" s="18" t="inlineStr">
-        <is>
-          <t>Défaut retenu pour les retenues (collinaire, pompage), le pompage sur cours d'eau, le réseau collectif et l'ASA. Un taux documenté de 45 % s'applique spécifiquement au forage individuel (voir ligne « Forage individuel »). Aides recensées CRA 71 2024 : PCAE petits équipements 40 % (+10 % JA/bio ; 400–5 000 €) ; PSN stockage d'eau 40 % ; FranceAgriMer sécheresse 30 % (+10 % JA/CUMA ; plafond 40 000 €, 150 000 € CUMA/ASA) ; CUCM forage/retenue 40 % (plafond 18 000 € HT) ; récupérateurs d'eau dépt. 71 65 % (plafond 35 000 €).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" hidden="1" ht="27.6" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>Général</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>taux_remplissage</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>Taux de remplissage d'une retenue</t>
-        </is>
-      </c>
-      <c r="D31" s="66" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G31" s="18" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H31" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="18" t="inlineStr">
-        <is>
-          <t>SGPE_2026</t>
-        </is>
-      </c>
-      <c r="K31" s="18" t="n"/>
-    </row>
+      <c r="K27" s="18" t="n"/>
+    </row>
+    <row r="28" ht="27.6" customHeight="1"/>
+    <row r="29" ht="27.6" customHeight="1"/>
+    <row r="30" hidden="1" ht="96.59999999999999" customHeight="1"/>
+    <row r="31" hidden="1" ht="27.6" customHeight="1"/>
     <row r="32" ht="27.6" customHeight="1"/>
     <row r="33" ht="55.2" customHeight="1"/>
     <row r="34" ht="27.6" customHeight="1"/>
@@ -24605,7 +24405,7 @@
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>Prélèvement en retenue taxé hors ZRE (1 = oui)</t>
+          <t>Retenue par pompage taxée au taux hors ZRE (1 = oui)</t>
         </is>
       </c>
       <c r="D8" s="65" t="n">
@@ -24637,7 +24437,11 @@
           <t>AEAG_REDEV</t>
         </is>
       </c>
-      <c r="K8" s="18" t="n"/>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>Ne concerne que la retenue par pompage : pour une retenue collinaire, le tarif de catégorie 1 s'applique d'office, quelle que soit la localisation (art. L213-10-9 du Code de l'environnement).</t>
+        </is>
+      </c>
     </row>
     <row r="9" hidden="1">
       <c r="A9" s="18" t="inlineStr">
@@ -24950,7 +24754,7 @@
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>Prélèvement en retenue taxé hors ZRE (1 = oui)</t>
+          <t>Retenue par pompage taxée au taux hors ZRE (1 = oui)</t>
         </is>
       </c>
       <c r="D15" s="65" t="n">
@@ -24982,7 +24786,11 @@
           <t>SGPE_2026</t>
         </is>
       </c>
-      <c r="K15" s="18" t="n"/>
+      <c r="K15" s="18" t="inlineStr">
+        <is>
+          <t>Ne concerne que la retenue par pompage : pour une retenue collinaire, le tarif de catégorie 1 s'applique d'office, quelle que soit la localisation (art. L213-10-9 du Code de l'environnement).</t>
+        </is>
+      </c>
     </row>
     <row r="16" hidden="1">
       <c r="A16" s="18" t="inlineStr">
@@ -25295,7 +25103,7 @@
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>Prélèvement en retenue taxé hors ZRE (1 = oui)</t>
+          <t>Retenue par pompage taxée au taux hors ZRE (1 = oui)</t>
         </is>
       </c>
       <c r="D22" s="65" t="n">
@@ -25327,7 +25135,11 @@
           <t>SGPE_2026</t>
         </is>
       </c>
-      <c r="K22" s="18" t="n"/>
+      <c r="K22" s="18" t="inlineStr">
+        <is>
+          <t>Ne concerne que la retenue par pompage : pour une retenue collinaire, le tarif de catégorie 1 s'applique d'office, quelle que soit la localisation (art. L213-10-9 du Code de l'environnement).</t>
+        </is>
+      </c>
     </row>
     <row r="23" hidden="1">
       <c r="A23" s="18" t="inlineStr">
@@ -25640,7 +25452,7 @@
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>Prélèvement en retenue taxé hors ZRE (1 = oui)</t>
+          <t>Retenue par pompage taxée au taux hors ZRE (1 = oui)</t>
         </is>
       </c>
       <c r="D29" s="65" t="n">
@@ -25672,7 +25484,11 @@
           <t>SGPE_2026</t>
         </is>
       </c>
-      <c r="K29" s="18" t="n"/>
+      <c r="K29" s="18" t="inlineStr">
+        <is>
+          <t>Ne concerne que la retenue par pompage : pour une retenue collinaire, le tarif de catégorie 1 s'applique d'office, quelle que soit la localisation (art. L213-10-9 du Code de l'environnement).</t>
+        </is>
+      </c>
     </row>
     <row r="30" hidden="1" ht="27.6" customHeight="1">
       <c r="A30" s="18" t="inlineStr">
@@ -25985,7 +25801,7 @@
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>Prélèvement en retenue taxé hors ZRE (1 = oui)</t>
+          <t>Retenue par pompage taxée au taux hors ZRE (1 = oui)</t>
         </is>
       </c>
       <c r="D36" s="65" t="n">
@@ -26017,7 +25833,11 @@
           <t>SGPE_2026</t>
         </is>
       </c>
-      <c r="K36" s="18" t="n"/>
+      <c r="K36" s="18" t="inlineStr">
+        <is>
+          <t>Ne concerne que la retenue par pompage : pour une retenue collinaire, le tarif de catégorie 1 s'applique d'office, quelle que soit la localisation (art. L213-10-9 du Code de l'environnement).</t>
+        </is>
+      </c>
     </row>
     <row r="37" hidden="1">
       <c r="A37" s="18" t="inlineStr">
@@ -26330,7 +26150,7 @@
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>Prélèvement en retenue taxé hors ZRE (1 = oui)</t>
+          <t>Retenue par pompage taxée au taux hors ZRE (1 = oui)</t>
         </is>
       </c>
       <c r="D43" s="65" t="n">
@@ -26362,7 +26182,11 @@
           <t>SGPE_2026</t>
         </is>
       </c>
-      <c r="K43" s="18" t="n"/>
+      <c r="K43" s="18" t="inlineStr">
+        <is>
+          <t>Ne concerne que la retenue par pompage : pour une retenue collinaire, le tarif de catégorie 1 s'applique d'office, quelle que soit la localisation (art. L213-10-9 du Code de l'environnement).</t>
+        </is>
+      </c>
     </row>
     <row r="44" hidden="1" ht="41.4" customHeight="1">
       <c r="A44" s="18" t="inlineStr">
@@ -29731,7 +29555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -30020,7 +29844,11 @@
           <t>ARVALIS – Institut du végétal. (2018, juin). Les vrai-faux de l'irrigation. Perspectives Agricoles / Choisir &amp; Décider.</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>https://agreste.agriculture.gouv.fr/agreste-web/disaron/Chd2009/detail/</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -30038,7 +29866,11 @@
           <t>ARVALIS – Institut du végétal. (2025). Bilan de la campagne d'irrigation du maïs 2025.</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>https://draaf.auvergne-rhone-alpes.agriculture.gouv.fr/IMG/pdf/20_essentiel_pkgc2021.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="26.4" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
@@ -30202,7 +30034,11 @@
           <t>Chambre d'agriculture Hauts-de-France. (2023). Guide de l'irrigation – matériels, coûts et économies d'eau (canon-enrouleur, rampe, pivot, goutte-à-goutte).</t>
         </is>
       </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>https://www.lebetteravier.fr/2025/09/29/comparez-le-prix-des-betteraves-en-france-et-en-europe/</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="26.4" customHeight="1">
       <c r="A23" s="29" t="inlineStr">
@@ -30238,7 +30074,11 @@
           <t>Favre, M. &amp; Hardelin, J. (2025). Le prix de l'eau : état des lieux et perspectives pour une gestion durable de la ressource. Commissariat général au développement durable (CGDD), coll. Théma.</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>https://www.brl.fr/phototheque/photos/memento/2025/Memento%20irrigation%202024_Web.pdf?_t=1768474480</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="26.4" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
@@ -30934,6 +30774,37 @@
       <c r="D58" s="8" t="inlineStr">
         <is>
           <t>https://www.paysan-breton.fr/2016/10/sans-irrigation-le-haricot-ne-fait-pas-le-poids/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61">
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.terresinovia.fr/sites/default/files/2026-01/guide_culture_chanvre_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>CENV_L213_10_9</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Code de l'environnement, art. L213-10-9</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>Code de l'environnement. (2026). Article L213-10-9 : redevances pour prélèvement sur la ressource en eau (version en vigueur au 21 février 2026). Légifrance.</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>https://www.legifrance.gouv.fr/codes/section_lc/LEGITEXT000006074220/LEGISCTA000006195231/</t>
         </is>
       </c>
     </row>

--- a/referentiel/referentiel_irrigation.xlsx
+++ b/referentiel/referentiel_irrigation.xlsx
@@ -9,11 +9,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cultures" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipement" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acces_ressource" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ressources" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cartes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exemples" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Departements" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Territoire" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ressources" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cartes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exemples" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Departements" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1974,7 +1975,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tableau2" displayName="Tableau2" ref="A1:D61" headerRowCount="1" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tableau2" displayName="Tableau2" ref="A1:D69" headerRowCount="1" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:D61"/>
   <sortState ref="A2:F62">
     <sortCondition ref="A1:A62"/>
@@ -25464,6 +25465,716 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18.77734375" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="57" t="inlineStr">
+        <is>
+          <t>Objet</t>
+        </is>
+      </c>
+      <c r="B1" s="57" t="inlineStr">
+        <is>
+          <t>Code paramètre</t>
+        </is>
+      </c>
+      <c r="C1" s="57" t="inlineStr">
+        <is>
+          <t>Libellé</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>Valeur</t>
+        </is>
+      </c>
+      <c r="E1" s="57" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="F1" s="57" t="inlineStr">
+        <is>
+          <t>Variable (oui/non)</t>
+        </is>
+      </c>
+      <c r="G1" s="57" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="H1" s="58" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="I1" s="57" t="inlineStr">
+        <is>
+          <t>Réf. (id)</t>
+        </is>
+      </c>
+      <c r="J1" s="57" t="inlineStr">
+        <is>
+          <t>Précision / commentaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Tension</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>part_zre</t>
+        </is>
+      </c>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>Part de la commune en ZRE au-delà de laquelle la case ZRE est cochée</t>
+        </is>
+      </c>
+      <c r="D2" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F2" s="18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="18" t="inlineStr">
+        <is>
+          <t>SGPE_2026</t>
+        </is>
+      </c>
+      <c r="J2" s="18" t="inlineStr">
+        <is>
+          <t>Part de la surface communale en zone de répartition des eaux de l'origine de l'eau prélevée (souterraine pour un forage, superficielle sinon).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>Tension</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>jours_restriction_vigilance</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Jours de restriction (alerte renforcée ou crise) : seuil de vigilance</t>
+        </is>
+      </c>
+      <c r="D3" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>j/an</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="18" t="n">
+        <v>365</v>
+      </c>
+      <c r="I3" s="18" t="inlineStr">
+        <is>
+          <t>SGPE_2026</t>
+        </is>
+      </c>
+      <c r="J3" s="18" t="inlineStr">
+        <is>
+          <t>Moyenne 2016-2025 des jours au moins en alerte renforcée ; une seule année avec un jour de crise suffit aussi à signaler une vigilance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>Tension</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>jours_restriction_defavorable</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>Jours de restriction (alerte renforcée ou crise) : seuil défavorable</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>j/an</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="18" t="n">
+        <v>365</v>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>SGPE_2026</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="inlineStr">
+        <is>
+          <t>Environ un mois par an de restrictions fortes en moyenne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Tension</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>annees_crise_defavorable</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Années avec au moins un jour de crise : seuil défavorable</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>ans sur 10</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>SGPE_2026</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>Sur les dix années 2016-2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Sol</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>ru_faible</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>Réserve utile faible en deçà de</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="n">
+        <v>80</v>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>400</v>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>RU_FRANCE_2021</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>Moyenne nationale de l'ordre de 95 mm sur 0-200 cm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>Sol</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>ru_elevee</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Réserve utile élevée au-delà de</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="n">
+        <v>150</v>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>400</v>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>RU_FRANCE_2021</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>Acces</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>distance_cours_eau</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>Distance maximale à un cours d'eau permanent pour un pompage</t>
+        </is>
+      </c>
+      <c r="D8" s="36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>SGPE_2026</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>Mesurée depuis un point intérieur de la commune ; deux fois la distance d'amenée par défaut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>Acces</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>distance_cours_eau_large</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Distance maximale à un cours d'eau de plus de 5 m de large</t>
+        </is>
+      </c>
+      <c r="D9" s="36" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>SGPE_2026</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Acces</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>distance_canal</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Distance maximale à un canal</t>
+        </is>
+      </c>
+      <c r="D10" s="36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>SGPE_2026</t>
+        </is>
+      </c>
+      <c r="J10" s="18" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>Acces</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>sau_irriguee_collectif</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Part de la SAU irriguée signalant un réseau collectif probable</t>
+        </is>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>SGPE_2026</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>Recensement agricole 2020 ; moyenne nationale ≈ 6 % des communes renseignées.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Acces</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>rang_aquifere_max</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>Rang maximal de la première nappe pour un forage peu profond</t>
+        </is>
+      </c>
+      <c r="D12" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>rang</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>SGPE_2026</t>
+        </is>
+      </c>
+      <c r="J12" s="18" t="inlineStr">
+        <is>
+          <t>1 = nappe affleurante, 2 = sous une première formation (BDLISA, niveau local).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>Projections</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>baisse_debit_vigilance</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Baisse du débit (2041-2070) ou de la recharge (+2,7 °C) : seuil de vigilance</t>
+        </is>
+      </c>
+      <c r="D13" s="36" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>-100</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>EXPLORE2_2025</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>Changement médian par rapport à 1976-2005 (Explore2, RCP4.5) du débit d'étiage, d'été ou d'hiver à la station la plus proche ; horizon de la durée d'amortissement des ouvrages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Projections</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>baisse_debit_defavorable</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>Baisse du débit (2041-2070) ou de la recharge (+2,7 °C) : seuil défavorable</t>
+        </is>
+      </c>
+      <c r="D14" s="36" t="n">
+        <v>-30</v>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>-100</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>EXPLORE2_2025</t>
+        </is>
+      </c>
+      <c r="J14" s="18" t="inlineStr">
+        <is>
+          <t>Ordre de grandeur de la baisse médiane des étiages projetée dans le sud de la France.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Projections</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>hausse_besoin_vigilance</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Hausse du besoin en eau entre 2021-2050 et 2071-2100 : vigilance</t>
+        </is>
+      </c>
+      <c r="D15" s="36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="18" t="inlineStr">
+        <is>
+          <t>SGPE_2026</t>
+        </is>
+      </c>
+      <c r="J15" s="18" t="inlineStr">
+        <is>
+          <t>Besoin d'irrigation de la méthode SGPE (DRIAS, RCP4.5).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
@@ -27474,7 +28185,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28069,7 +28780,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28535,7 +29246,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30416,13 +31127,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -30891,7 +31602,11 @@
           <t>Chambres d'agriculture France (APCA). (2025). Coûts des opérations culturales des matériels agricoles [Barème]. Section « Matériels et installation d'irrigation » : enrouleurs, pivots et rampes, forage-réserve, station d'irrigation, canalisations fixes et mobiles (p. 55-57). Coûts établis par la Chambre d'agriculture du Loiret.</t>
         </is>
       </c>
-      <c r="D22" s="30" t="n"/>
+      <c r="D22" s="30" t="inlineStr">
+        <is>
+          <t>https://www.lebetteravier.fr/2025/09/29/comparez-le-prix-des-betteraves-en-france-et-en-europe/</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="26.4" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
@@ -30968,7 +31683,11 @@
 cotisations d'assurance récolte 2026 et pour l’indemnisation des pertes de récolte 2026 fondée sur la solidarité nationale</t>
         </is>
       </c>
-      <c r="D26" s="8" t="n"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>https://hautsdefrance.chambres-agriculture.fr/actualites/actualite/prix-de-la-paille-et-des-fourrages-bareme-pour-lannee-2025</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="26.4" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
@@ -31194,7 +31913,11 @@
           <t>Ministère de l'Agriculture, des Pêcheries et de l'Alimentation du Québec. (s.d.). Irrigation de la pomme de terre : gains de rendement vendable selon le cultivar.</t>
         </is>
       </c>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>https://draaf.occitanie.agriculture.gouv.fr/l-irrigation-vectrice-de-la-production-fruitiere-analyses-etudes-no4-octobre-a5055.html</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="26.4" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
@@ -31688,13 +32411,182 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="26.4" customHeight="1"/>
-    <row r="64" ht="26.4" customHeight="1"/>
-    <row r="65" ht="39.6" customHeight="1"/>
-    <row r="66" ht="22.8" customHeight="1"/>
-    <row r="67" ht="79.2" customHeight="1"/>
-    <row r="68" ht="26.4" customHeight="1"/>
-    <row r="69" ht="26.4" customHeight="1"/>
+    <row r="62" ht="26.4" customHeight="1">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>SANDRE_ZRE</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Sandre, 2025a</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>Sandre. (2025). Zones de répartition des eaux (ZRE) [Jeu de données géographiques]. Service d'administration nationale des données et référentiels sur l'eau, Office français de la biodiversité.</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sandre.eaufrance.fr/atlas/srv/fre/catalog.search#/metadata/e5325942-18f6-472c-973a-1f35bb207eb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>SANDRE_BASSINS</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Sandre, 2025b</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>Sandre. (2025). Circonscriptions administratives de bassin [Jeu de données géographiques]. Service d'administration nationale des données et référentiels sur l'eau.</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sandre.eaufrance.fr/atlas/srv/fre/catalog.search#/home</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="26.4" customHeight="1">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>SANDRE_SAGE</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Sandre, 2025c</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>Sandre. (2025). Schémas d'aménagement et de gestion des eaux (SAGE) [Jeu de données géographiques]. Service d'administration nationale des données et référentiels sur l'eau.</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sandre.eaufrance.fr/atlas/srv/fre/catalog.search#/home</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="39.6" customHeight="1">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>VIGIEAU_2026</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>Ministère de la Transition écologique, 2026</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Ministère de la Transition écologique. (2026). Donnée sécheresse VigiEau : historique des restrictions par commune depuis 2010 [Jeu de données]. data.gouv.fr.</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>https://www.data.gouv.fr/datasets/donnee-secheresse-vigieau</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22.8" customHeight="1">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>AGRESTE_RA2020</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Agreste, 2022</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>Agreste. (2022). Recensement agricole 2020 : part de la superficie irriguée dans la SAU, par commune [Jeu de données]. Ministère de l'Agriculture et de la Souveraineté alimentaire.</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>https://agreste.agriculture.gouv.fr/agreste-web/disaron/RA2020_CARTO/detail/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="79.2" customHeight="1">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>BDTOPAGE</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>IGN &amp; OFB, 2026</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>IGN, &amp; Office français de la biodiversité. (2026). BD TOPAGE : tronçons hydrographiques, France métropolitaine [Jeu de données géographiques]. Sandre.</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sandre.eaufrance.fr/atlas/srv/fre/catalog.search#/home</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="26.4" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>BDLISA</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>BRGM, 2025</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>BRGM. (2025). BDLISA, référentiel hydrogéologique français : entités hydrogéologiques de niveau local, France métropolitaine [Jeu de données géographiques].</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>https://bdlisa.eaufrance.fr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="26.4" customHeight="1">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>ROE_OFB</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>OFB, 2025</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>Office français de la biodiversité. (2025). Référentiel des obstacles à l'écoulement (ROE) [Jeu de données géographiques]. Sandre.</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sandre.eaufrance.fr/atlas/srv/fre/catalog.search#/home</t>
+        </is>
+      </c>
+    </row>
     <row r="70" ht="26.4" customHeight="1"/>
   </sheetData>
   <hyperlinks>
